--- a/DEF_AnalisisGrafico/Analisis8mins_Correct_II/Graficas/AnalisisGrafico_II_Rest_Working_2025-02-21.xlsx
+++ b/DEF_AnalisisGrafico/Analisis8mins_Correct_II/Graficas/AnalisisGrafico_II_Rest_Working_2025-02-21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martaguzman/4_Carrera/TFG_MartaGuzman_DEF/DEF_AnalisisGrafico/Analisis8mins_Correct_II/Graficas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58A90AC-6216-3A45-B8E2-99E6F3923900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB327905-6A74-8046-AB13-E0AA08607CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{7C695524-3981-4A54-8184-D123407E7D5E}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" xr2:uid="{7C695524-3981-4A54-8184-D123407E7D5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
